--- a/Result/profitability/6272.xlsx
+++ b/Result/profitability/6272.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM44"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4949999999999999</v>
+        <v>0.465</v>
       </c>
       <c r="N2" t="n">
-        <v>24.54875</v>
+        <v>24.00125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0.58875</v>
+        <v>0.4662500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>24.67</v>
+        <v>23.8425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>0.40125</v>
+        <v>0.29375</v>
       </c>
       <c r="N4" t="n">
-        <v>24.19125</v>
+        <v>23.46125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.42125</v>
+        <v>0.32875</v>
       </c>
       <c r="N5" t="n">
-        <v>24.60125</v>
+        <v>23.8375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.39125</v>
+        <v>0.225</v>
       </c>
       <c r="N6" t="n">
-        <v>24.5725</v>
+        <v>23.72875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39125</v>
+        <v>0.3275</v>
       </c>
       <c r="N7" t="n">
-        <v>24.82125</v>
+        <v>24.405</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -6016,6 +6016,133 @@
       </c>
       <c r="AM44" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6272</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>863</v>
+      </c>
+      <c r="D45" t="n">
+        <v>683</v>
+      </c>
+      <c r="E45" t="n">
+        <v>180</v>
+      </c>
+      <c r="F45" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.5987499999999999</v>
+      </c>
+      <c r="N45" t="n">
+        <v>24.99875</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="X45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>-0.1600000000000001</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-0.007615421227986641</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>-6.109999999999999</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>-0.2266320474777448</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
